--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q40_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009165965900040656</v>
+        <v>0.00912515713102079</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009165965900040656</v>
+        <v>0.00912515713102079</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003887808942296298</v>
+        <v>0.00439063615706513</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008686629638890487</v>
+        <v>0.008560711741118604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008686629638890487</v>
+        <v>0.008560711741118604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002671286076416105</v>
+        <v>0.002998003805446544</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01059343373277867</v>
+        <v>0.01053739426121187</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01059343373277867</v>
+        <v>0.01053739426121187</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002219410461513755</v>
+        <v>0.002376896263471683</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0164911523945127</v>
+        <v>0.0167390879130013</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0164911523945127</v>
+        <v>0.0167390879130013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003002674412403997</v>
+        <v>0.002717270492760728</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02520142580692479</v>
+        <v>0.02560737080292864</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02520142580692479</v>
+        <v>0.02560737080292864</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0062319792489626</v>
+        <v>0.006059689168486339</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03421271924814367</v>
+        <v>0.03459151381803179</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03421271924814367</v>
+        <v>0.03459151381803179</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00530058368922263</v>
+        <v>0.004876122269806266</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04584240221753676</v>
+        <v>0.04636494309962553</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04584240221753676</v>
+        <v>0.04636494309962553</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004429452471789243</v>
+        <v>0.003308468795534247</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05693888702941222</v>
+        <v>0.05773032277221633</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05693888702941222</v>
+        <v>0.05773032277221633</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005894063423433548</v>
+        <v>0.004545338303112432</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0644439608929603</v>
+        <v>0.0654005307829538</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0644439608929603</v>
+        <v>0.0654005307829538</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00761001593420745</v>
+        <v>0.005665020802597466</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06775227841395201</v>
+        <v>0.06869926723974373</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06775227841395201</v>
+        <v>0.06869926723974373</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009119269207794135</v>
+        <v>0.006684374622380711</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0671340953299677</v>
+        <v>0.06797621014404136</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0671340953299677</v>
+        <v>0.06797621014404136</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01012480689611379</v>
+        <v>0.007327995050610731</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06475767443972565</v>
+        <v>0.06553014129871057</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06475767443972565</v>
+        <v>0.06553014129871057</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01036258456651444</v>
+        <v>0.007459573711835293</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06166924584593483</v>
+        <v>0.062432534826814</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06166924584593483</v>
+        <v>0.062432534826814</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01025430922102418</v>
+        <v>0.007583984637122605</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05745142329318535</v>
+        <v>0.0581871621423185</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05745142329318535</v>
+        <v>0.0581871621423185</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01022505244100919</v>
+        <v>0.007916423177721194</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0556608954136664</v>
+        <v>0.05641977651298359</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0556608954136664</v>
+        <v>0.05641977651298359</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01029437278086205</v>
+        <v>0.008190691764563791</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05203520472285234</v>
+        <v>0.05277854544298297</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05203520472285234</v>
+        <v>0.05277854544298297</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01001845449054992</v>
+        <v>0.008363063311551308</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.04956234522078284</v>
+        <v>0.05031061998555068</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04956234522078284</v>
+        <v>0.05031061998555068</v>
       </c>
       <c r="D18" t="n">
-        <v>0.010225494072997</v>
+        <v>0.00862500234347003</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05017763214449331</v>
+        <v>0.05095964383984566</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05017763214449331</v>
+        <v>0.05095964383984566</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01043929566513488</v>
+        <v>0.008859364693705775</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.04670369541452517</v>
+        <v>0.04746839917448065</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04670369541452517</v>
+        <v>0.04746839917448065</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01079554208695003</v>
+        <v>0.009247717746493246</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.04517513541591965</v>
+        <v>0.04606851557416652</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04517513541591965</v>
+        <v>0.04606851557416652</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01061934079359038</v>
+        <v>0.009231911487360146</v>
       </c>
     </row>
   </sheetData>
